--- a/uploadtemplate.xlsx
+++ b/uploadtemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhengyangliu/Desktop/NFSBot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A977B2F6-35F9-404B-92A0-5E5294C3EDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44436AAE-0A5F-4F4B-8C3A-02D7047A2D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Name</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>toolbats</t>
+  </si>
+  <si>
+    <t>source</t>
   </si>
 </sst>
 </file>
@@ -344,10 +347,10 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -399,8 +402,11 @@
       <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R1" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="3"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
@@ -410,7 +416,7 @@
       <c r="G2" s="1"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -419,7 +425,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -428,7 +434,7 @@
       <c r="G4" s="1"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -437,7 +443,7 @@
       <c r="G5" s="1"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -446,7 +452,7 @@
       <c r="G6" s="1"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
@@ -455,7 +461,7 @@
       <c r="G7" s="1"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -464,7 +470,7 @@
       <c r="G8" s="1"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -473,7 +479,7 @@
       <c r="G9" s="1"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -482,7 +488,7 @@
       <c r="G10" s="1"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -491,7 +497,7 @@
       <c r="G11" s="1"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -500,7 +506,7 @@
       <c r="G12" s="1"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
@@ -509,7 +515,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -518,7 +524,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -527,7 +533,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
